--- a/results/run_1/metrics_rc.xlsx
+++ b/results/run_1/metrics_rc.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -502,41 +502,176 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1032112804944665</v>
+        <v>0.2322888711374143</v>
       </c>
       <c r="C2" t="n">
-        <v>0.3212651249271644</v>
+        <v>0.4819635578935552</v>
       </c>
       <c r="D2" t="n">
-        <v>0.293421082839479</v>
+        <v>0.4402194931285253</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7856229770131442</v>
+        <v>1.177553377988573</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.2925793702461091</v>
+        <v>-0.4389499083256129</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8008530208785685</v>
+        <v>0.5479386233250889</v>
       </c>
       <c r="H2" t="n">
-        <v>1.410323091839259</v>
+        <v>2.115438827342663</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01760859260085675</v>
+        <v>0.03961184911835037</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1326973722454848</v>
+        <v>0.1990272572246082</v>
       </c>
       <c r="K2" t="n">
-        <v>1.937163798433682e-05</v>
+        <v>3.576850390521867e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0819668999993155</v>
+        <v>0.06975969999984954</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>RC basé IDF, sans airgap</t>
+          <t>RC basé IDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>165.9851715752373</v>
+      </c>
+      <c r="C3" t="n">
+        <v>12.88352325938977</v>
+      </c>
+      <c r="D3" t="n">
+        <v>11.8693040216461</v>
+      </c>
+      <c r="E3" t="n">
+        <v>26.82933972340649</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-11.86662367102372</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-322.0266039113627</v>
+      </c>
+      <c r="H3" t="n">
+        <v>56.54847734754402</v>
+      </c>
+      <c r="I3" t="n">
+        <v>25.1684142255368</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5.016813154337801</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.0001243422839398079</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.2720943999993324</v>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>RC basé IDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>165.1038050977146</v>
+      </c>
+      <c r="C4" t="n">
+        <v>12.84927255130479</v>
+      </c>
+      <c r="D4" t="n">
+        <v>11.79216552533927</v>
+      </c>
+      <c r="E4" t="n">
+        <v>26.87338382340649</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-11.78882850359828</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-354.0229126777968</v>
+      </c>
+      <c r="H4" t="n">
+        <v>56.59138033450032</v>
+      </c>
+      <c r="I4" t="n">
+        <v>26.12732761046336</v>
+      </c>
+      <c r="J4" t="n">
+        <v>5.111489764292144</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0001213826034649914</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.2671637999992527</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>RC basé IDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>165.1038050977146</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12.84927255130479</v>
+      </c>
+      <c r="D5" t="n">
+        <v>11.79216552533927</v>
+      </c>
+      <c r="E5" t="n">
+        <v>26.87338382340649</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-11.78882850359828</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-354.0229126777968</v>
+      </c>
+      <c r="H5" t="n">
+        <v>56.59138033450032</v>
+      </c>
+      <c r="I5" t="n">
+        <v>26.12732761046336</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5.111489764292144</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0001213826034649914</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.2483408999978565</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>RC basé IDF</t>
         </is>
       </c>
     </row>

--- a/results/run_1/metrics_rc.xlsx
+++ b/results/run_1/metrics_rc.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,6 +675,411 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>78.095579192869</v>
+      </c>
+      <c r="C6" t="n">
+        <v>8.837170315936488</v>
+      </c>
+      <c r="D6" t="n">
+        <v>7.909361799192661</v>
+      </c>
+      <c r="E6" t="n">
+        <v>16.09857325079148</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-7.891207713589026</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-150.9836561287925</v>
+      </c>
+      <c r="H6" t="n">
+        <v>38.78818550190685</v>
+      </c>
+      <c r="I6" t="n">
+        <v>15.82442001386205</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.97799195749087</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.931158374895004e-05</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.1885812000000442</v>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>RC basé IDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>78.095579192869</v>
+      </c>
+      <c r="C7" t="n">
+        <v>8.837170315936488</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7.909361799192661</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16.09857325079148</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-7.891207713589026</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-150.9836561287925</v>
+      </c>
+      <c r="H7" t="n">
+        <v>38.78818550190685</v>
+      </c>
+      <c r="I7" t="n">
+        <v>15.82442001386205</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.97799195749087</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.931158374895004e-05</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.2007727999989584</v>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>RC basé IDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>78.095579192869</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8.837170315936488</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7.909361799192661</v>
+      </c>
+      <c r="E8" t="n">
+        <v>16.09857325079148</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-7.891207713589026</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-150.9836561287925</v>
+      </c>
+      <c r="H8" t="n">
+        <v>38.78818550190685</v>
+      </c>
+      <c r="I8" t="n">
+        <v>15.82442001386205</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.97799195749087</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.287438916596669e-05</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2010350999989896</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>RC basé IDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>78.095579192869</v>
+      </c>
+      <c r="C9" t="n">
+        <v>8.837170315936488</v>
+      </c>
+      <c r="D9" t="n">
+        <v>7.909361799192661</v>
+      </c>
+      <c r="E9" t="n">
+        <v>16.09857325079148</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-7.891207713589026</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-150.9836561287925</v>
+      </c>
+      <c r="H9" t="n">
+        <v>38.78818550190685</v>
+      </c>
+      <c r="I9" t="n">
+        <v>15.82442001386205</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.97799195749087</v>
+      </c>
+      <c r="K9" t="n">
+        <v>5.287438916596669e-05</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2157976999988023</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>RC basé IDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>21.39197102571284</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.625145514004164</v>
+      </c>
+      <c r="D10" t="n">
+        <v>3.835726776457968</v>
+      </c>
+      <c r="E10" t="n">
+        <v>15.18079305261628</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-1.533399072931496</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-40.63142141835741</v>
+      </c>
+      <c r="H10" t="n">
+        <v>20.30072927835095</v>
+      </c>
+      <c r="I10" t="n">
+        <v>19.04065830884566</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.36356027904344</v>
+      </c>
+      <c r="K10" t="n">
+        <v>8.378181679724119e-05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2553695999995398</v>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>RC basé IDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>81.72822097852782</v>
+      </c>
+      <c r="C11" t="n">
+        <v>9.040366197147536</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8.050622879033996</v>
+      </c>
+      <c r="E11" t="n">
+        <v>18.26281117235354</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-7.909168930317047</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-158.053226336181</v>
+      </c>
+      <c r="H11" t="n">
+        <v>39.68005464687787</v>
+      </c>
+      <c r="I11" t="n">
+        <v>19.1732678102353</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.378729017675711</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8.370746816155007e-05</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.237732400000823</v>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>RC basé IDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>81.72822097852782</v>
+      </c>
+      <c r="C12" t="n">
+        <v>9.040366197147536</v>
+      </c>
+      <c r="D12" t="n">
+        <v>8.050622879033996</v>
+      </c>
+      <c r="E12" t="n">
+        <v>18.26281117235354</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-7.909168930317047</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-158.053226336181</v>
+      </c>
+      <c r="H12" t="n">
+        <v>39.68005464687787</v>
+      </c>
+      <c r="I12" t="n">
+        <v>19.1732678102353</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.378729017675711</v>
+      </c>
+      <c r="K12" t="n">
+        <v>8.370746816155007e-05</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.3139443999998548</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>RC basé IDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>81.72822097852782</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9.040366197147536</v>
+      </c>
+      <c r="D13" t="n">
+        <v>8.050622879033996</v>
+      </c>
+      <c r="E13" t="n">
+        <v>18.26281117235354</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-7.909168930317047</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-158.053226336181</v>
+      </c>
+      <c r="H13" t="n">
+        <v>39.68005464687787</v>
+      </c>
+      <c r="I13" t="n">
+        <v>19.1732678102353</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.378729017675711</v>
+      </c>
+      <c r="K13" t="n">
+        <v>8.370746816155007e-05</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2054657999997289</v>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>RC basé IDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>78.095579192869</v>
+      </c>
+      <c r="C14" t="n">
+        <v>8.837170315936488</v>
+      </c>
+      <c r="D14" t="n">
+        <v>7.909361799192661</v>
+      </c>
+      <c r="E14" t="n">
+        <v>16.09857325079148</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-7.891207713589026</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-150.9836561287925</v>
+      </c>
+      <c r="H14" t="n">
+        <v>38.78818550190685</v>
+      </c>
+      <c r="I14" t="n">
+        <v>15.82442001386205</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.97799195749087</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.287438916596669e-05</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2982369000001199</v>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>RC basé IDF</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/results/run_1/metrics_rc.xlsx
+++ b/results/run_1/metrics_rc.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1080,6 +1080,96 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.003322372264069098</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.05764002310954688</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.04103192872424281</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.3579747416810335</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.03039757112886944</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9935342740607098</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2529941131395536</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.002398359933534421</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.04897305313674472</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.267363527181593e-05</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3665927999991254</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>RC pas de temps 15min</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RC_model</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3.517444047020685</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.875485016474588</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.34232044078388</v>
+      </c>
+      <c r="E16" t="n">
+        <v>5.682403771136123</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.251242361947994</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-5.845358499041014</v>
+      </c>
+      <c r="H16" t="n">
+        <v>8.231895874637852</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.95183659868749</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.397081457427408</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0003297123753451451</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.334514099999069</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>RC déroulement 24h</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
